--- a/fixtures/acceptance/T10_old_value_mismatch/Output/IntegrationReport_T10_RUN.xlsx
+++ b/fixtures/acceptance/T10_old_value_mismatch/Output/IntegrationReport_T10_RUN.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,37 +489,97 @@
           <t>MORT_TABLE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>value_update</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>20|1|PROD_A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>old_value mismatch: change log has '0.0012', production has '0.0099'.</t>
+          <t>Validation passed.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CR_T10_Mismatch</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MORT_TABLE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Applied 1 change row(s).</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Wrote 1 table(s) to C:\Chun\Python\Prophet Table Integration\fixtures\acceptance\T10_old_value_mismatch\Output\New_Production_Tables</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
@@ -547,7 +607,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>SUCCESS</t>
         </is>
       </c>
     </row>
@@ -570,7 +630,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -580,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
